--- a/tests/fixtures/e2e/acuan/rencana.xlsx
+++ b/tests/fixtures/e2e/acuan/rencana.xlsx
@@ -453,7 +453,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Dibuat: 2025-09-10 20:00:00 WIB — hash8 44b5deb5 — versi 0.1.0 — REPLAY (--tanggal)</t>
+          <t>Dibuat: 2025-09-10 20:00:00 WIB — hash8 2d1ece58 — versi 0.1.0 — REPLAY (--tanggal)</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>PB</t>
+          <t>TP</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -826,7 +826,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>PB</t>
+          <t>TP</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>PB</t>
+          <t>TP</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1132,7 +1132,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>PB</t>
+          <t>TP</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>PB</t>
+          <t>TP</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>PB</t>
+          <t>TP</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>PB</t>
+          <t>TP</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -2244,21 +2244,21 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Penyimpangan PB: sampel jurnal 0 &lt; 20: belum diuji</t>
+          <t>Penyimpangan TP: sampel jurnal 0 &lt; 20: belum diuji</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Penyimpangan BO: sampel jurnal 0 &lt; 20: belum diuji</t>
+          <t>Penyimpangan TB: sampel jurnal 0 &lt; 20: belum diuji</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Penyimpangan MR: sampel jurnal 0 &lt; 20: belum diuji</t>
+          <t>Penyimpangan PJ: sampel jurnal 0 &lt; 20: belum diuji</t>
         </is>
       </c>
     </row>

--- a/tests/fixtures/e2e/acuan/rencana.xlsx
+++ b/tests/fixtures/e2e/acuan/rencana.xlsx
@@ -453,7 +453,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Dibuat: 2025-09-10 20:00:00 WIB — hash8 2d1ece58 — versi 0.1.0 — REPLAY (--tanggal)</t>
+          <t>Dibuat: 2025-09-10 20:00:00 WIB — hash8 ccc84033 — versi 0.1.0 — REPLAY (--tanggal)</t>
         </is>
       </c>
     </row>
@@ -488,7 +488,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BELI UJIGAP 4 lot, limit 1.363 — tarik jika tidak terisi saat pembukaan</t>
+          <t>BELI UJIGAP 4 lot, limit 1.364 — tarik jika tidak terisi saat pembukaan</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Rp 1.000.000</t>
+          <t>Rp 1.500.000</t>
         </is>
       </c>
     </row>
@@ -568,7 +568,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -592,7 +592,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BOLEH BELI (K3): Tren IHSG naik dan breadth sehat</t>
+          <t>BOLEH BELI (K1): IHSG dalam tren turun: strategi tren turun aktif</t>
         </is>
       </c>
     </row>
@@ -830,13 +830,13 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>68.2</v>
+        <v>55.9</v>
       </c>
       <c r="F4" t="n">
         <v>1352.760221</v>
       </c>
       <c r="G4" t="n">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="H4" t="n">
         <v>1309</v>
@@ -847,7 +847,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>1471</v>
+        <v>1474</v>
       </c>
       <c r="K4" t="n">
         <v>4</v>
@@ -856,17 +856,17 @@
         <v>400</v>
       </c>
       <c r="M4" t="n">
-        <v>545200</v>
+        <v>545600</v>
       </c>
       <c r="N4" t="n">
-        <v>817.8</v>
+        <v>818.4</v>
       </c>
       <c r="O4" t="n">
-        <v>24249.09</v>
+        <v>24649.69</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="Q4" t="n">
@@ -874,13 +874,13 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Pasang order BELI limit di 1.363, 4 lot, sebelum pra-pembukaan t+1. Segera setelah harga pembukaan terbentuk, cek order Anda. Jika belum terisi (open &gt; harga_maks), tarik (withdraw) order; jangan biarkan antre sepanjang hari, karena bisa terisi belakangan di harga yang tidak diuji backtest. Jika hanya terisi sebagian, tarik sisanya dan catat lot yang terisi saja.</t>
+          <t>Pasang order BELI limit di 1.364, 4 lot, sebelum pra-pembukaan t+1. Segera setelah harga pembukaan terbentuk, cek order Anda. Jika belum terisi (open &gt; harga_maks), tarik (withdraw) order; jangan biarkan antre sepanjang hari, karena bisa terisi belakangan di harga yang tidak diuji backtest. Jika hanya terisi sebagian, tarik sisanya dan catat lot yang terisi saja.</t>
         </is>
       </c>
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr">
         <is>
-          <t>Pasang order otomatis stop di 1.309 (dan target di 1.471) hari itu juga. Jika harga isi sudah ≤ stop, stop telah terlewati: jual segera. Perbarui portfolio.csv dan akun.yaml (§19.6).</t>
+          <t>Pasang order otomatis stop di 1.309 (dan target di 1.474) hari itu juga. Jika harga isi sudah ≤ stop, stop telah terlewati: jual segera. Perbarui portfolio.csv dan akun.yaml (§19.6).</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -1203,17 +1203,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>UJIGAP</t>
+          <t>UJIMAHAL2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ujigap Tbk (FIKTIF – KHUSUS UJI)</t>
+          <t>Ujimahal2 Tbk (FIKTIF – KHUSUS UJI)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Sektor Fiktif F</t>
+          <t>Sektor Fiktif E</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1223,15 +1223,19 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>68.15403</t>
+          <t>66.862812</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>REKOMENDASI</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>TIDAK_TERJANGKAU</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>nilai 1 lot Rp 1.552.325 &gt; alokasi maks Rp 1.500.000</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>BOLEH_BELI</t>
@@ -1239,52 +1243,40 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>1352.760221</t>
+          <t>15456.388298</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>1363</t>
+          <t>15500</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>1309</t>
+          <t>15290</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>1471</t>
+          <t>15920</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>545200.00</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>546017.80</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>24249.09</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
-          <t>40897731829.50</t>
+          <t>77305612099.75</t>
         </is>
       </c>
       <c r="T5" t="inlineStr"/>
@@ -1297,17 +1289,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>UJIMAHAL2</t>
+          <t>UJISEKTOR</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ujimahal2 Tbk (FIKTIF – KHUSUS UJI)</t>
+          <t>Ujisektor Tbk (FIKTIF – KHUSUS UJI)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Sektor Fiktif E</t>
+          <t>Sektor Fiktif A</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1317,17 +1309,17 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>64.340636</t>
+          <t>60.315845</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>TIDAK_TERJANGKAU</t>
+          <t>BATAS_SEKTOR</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>nilai 1 lot Rp 1.051.575 &gt; alokasi maks Rp 1.000.000</t>
+          <t>sektor Sektor Fiktif A sudah mencapai 1 posisi</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1337,40 +1329,32 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>10457.7189</t>
+          <t>3368.690004</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>10500</t>
+          <t>3396</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>10290</t>
+          <t>3272</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>10920</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>3644</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
-          <t>52488717525.25</t>
+          <t>20444902751.40</t>
         </is>
       </c>
       <c r="T6" t="inlineStr"/>
@@ -1383,17 +1367,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>UJISEKTOR</t>
+          <t>UJIGAP</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ujisektor Tbk (FIKTIF – KHUSUS UJI)</t>
+          <t>Ujigap Tbk (FIKTIF – KHUSUS UJI)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Sektor Fiktif A</t>
+          <t>Sektor Fiktif F</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1403,19 +1387,15 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>60.315845</t>
+          <t>55.887967</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>BATAS_SEKTOR</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>sektor Sektor Fiktif A sudah mencapai 1 posisi</t>
-        </is>
-      </c>
+          <t>REKOMENDASI</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>BOLEH_BELI</t>
@@ -1423,32 +1403,52 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>3368.690004</t>
+          <t>1352.760221</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>3396</t>
+          <t>1364</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>3272</t>
+          <t>1309</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>3644</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
+          <t>1474</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>545600.00</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>546418.40</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>24649.69</t>
+        </is>
+      </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>20444902751.40</t>
+          <t>13632577276.50</t>
         </is>
       </c>
       <c r="T7" t="inlineStr"/>
@@ -1565,7 +1565,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BOLEH BELI (K3): Tren IHSG naik dan breadth sehat</t>
+          <t>BOLEH BELI (K1): IHSG dalam tren turun: strategi tren turun aktif</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>10.377,56</t>
+          <t>4.302,20</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>11.082,53</t>
+          <t>3.920,57</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1846,17 +1846,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>11.289,61 vs 10.377,56</t>
+          <t>3.768,29 vs 4.302,20</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>tren turun bila ✓</t>
+          <t>keduanya ✓ → BOLEH BELI</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
     </row>
@@ -1873,17 +1873,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>11.082,53 vs 10.377,56</t>
+          <t>3.920,57 vs 4.302,20</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>tren turun bila ✓</t>
+          <t>keduanya ✓ → BOLEH BELI</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
     </row>
@@ -1900,123 +1900,15 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>65%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>&lt; 30% → JANGAN BELI</t>
+          <t>&lt; 30% → HATI-HATI bila K1 ✗</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>K3</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>IHSG close &gt; SMA200</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>11.289,61 vs 10.377,56</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>wajib ✓</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>K3</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>SMA50 &gt; SMA200</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>11.082,53 vs 10.377,56</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>wajib ✓</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>K3</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>IHSG close &gt; SMA50</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>11.289,61 vs 11.082,53</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>wajib ✓</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>K3</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Breadth</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>65%</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>≥ 50%</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -2188,7 +2080,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>pasar.jadwal_sesi — batas bar final = jadwal.jam_run 19:30 WIB; setiap run pada tanggal t+1 diberi banner. Cek jadwal perdagangan di idx.co.id.</t>
+          <t>pasar.jadwal_sesi — batas bar final = jadwal.jam_run 20:00 WIB; setiap run pada tanggal t+1 diberi banner. Cek jadwal perdagangan di idx.co.id.</t>
         </is>
       </c>
     </row>
